--- a/ibm6450/files/Relational_Training.xlsx
+++ b/ibm6450/files/Relational_Training.xlsx
@@ -2,31 +2,50 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-29040" yWindow="860" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1st Pass" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Garamond"/>
+      <family val="1"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <family val="1"/>
+      <color theme="0"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <family val="1"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +56,29 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -47,21 +88,36 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -134,114 +190,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="467886"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Aptos Narrow"/>
+        <a:cs typeface="Aptos Narrow"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Aptos Narrow"/>
+        <a:cs typeface="Aptos Narrow"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -253,160 +251,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -422,13 +391,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="21"/>
   <cols>
-    <col width="8.699999999999999" customWidth="1" min="1" max="1"/>
-    <col width="8.699999999999999" customWidth="1" min="2" max="2"/>
-    <col width="86.90000000000001" customWidth="1" min="3" max="3"/>
-    <col width="31.3" customWidth="1" min="4" max="4"/>
+    <col width="8.6640625" customWidth="1" style="2" min="1" max="2"/>
+    <col width="93.83203125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="43.6640625" customWidth="1" style="2" min="4" max="4"/>
+    <col width="45.83203125" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="8.6640625" customWidth="1" style="2" min="6" max="24"/>
+    <col width="12.6640625" customWidth="1" style="2" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,204 +423,1000 @@
           <t>High Relational = 1, 0 otherwise</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Your ticket here says your flight is scheduled to leave at 9. That is what you were booked for</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="6" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Right but your original reservation was for 9....You are trying to go standby</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="6" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" ht="66" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>And everybody else is trying to go standby before you that I am dealing with. I can put you on the list but we have a lot from these other flights that are going to be ahead of you</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="6" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>I am going to see if you are on this list right now. I understand you checked in downstairs at 9:00…...........</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Right but what I am saying right now it is 9:50 …........You were saying you have been sitting here for an hour trying to get on the standby list. It has only been 40 minutes</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Did you ask to be put on standby</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Please do not raise your voice</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>I understand that. Everybody needs to get there. You are going to have to wait with everybody else</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>It is a Friday night. You have got weather and you booked your flight for 9.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>You were originally scheduled for 9 though. Just bear with us that is all I can ask</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>You missed your first flight when you got here at 9…...?</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="9" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>I do not know what to say at this point If you missed your original flight. You would be there already had you been here on time right? I cannot put you ahead of everybody else That is not right</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>All right. It looks like there is a seat available that I can get you….. Also you have got such a nice smile. You should use it more</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>You were wrong by not using that earlier!</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="6" t="n"/>
     </row>
+    <row r="225" customFormat="1" s="2"/>
+    <row r="226" customFormat="1" s="2"/>
+    <row r="227" customFormat="1" s="2"/>
+    <row r="228" customFormat="1" s="2"/>
+    <row r="229" customFormat="1" s="2"/>
+    <row r="230" customFormat="1" s="2"/>
+    <row r="231" customFormat="1" s="2"/>
+    <row r="232" customFormat="1" s="2"/>
+    <row r="233" customFormat="1" s="2"/>
+    <row r="234" customFormat="1" s="2"/>
+    <row r="235" customFormat="1" s="2"/>
+    <row r="236" customFormat="1" s="2"/>
+    <row r="237" customFormat="1" s="2"/>
+    <row r="238" customFormat="1" s="2"/>
+    <row r="239" customFormat="1" s="2"/>
+    <row r="240" customFormat="1" s="2"/>
+    <row r="241" customFormat="1" s="2"/>
+    <row r="242" customFormat="1" s="2"/>
+    <row r="243" customFormat="1" s="2"/>
+    <row r="244" customFormat="1" s="2"/>
+    <row r="245" customFormat="1" s="2"/>
+    <row r="246" customFormat="1" s="2"/>
+    <row r="247" customFormat="1" s="2"/>
+    <row r="248" customFormat="1" s="2"/>
+    <row r="249" customFormat="1" s="2"/>
+    <row r="250" customFormat="1" s="2"/>
+    <row r="251" customFormat="1" s="2"/>
+    <row r="252" customFormat="1" s="2"/>
+    <row r="253" customFormat="1" s="2"/>
+    <row r="254" customFormat="1" s="2"/>
+    <row r="255" customFormat="1" s="2"/>
+    <row r="256" customFormat="1" s="2"/>
+    <row r="257" customFormat="1" s="2"/>
+    <row r="258" customFormat="1" s="2"/>
+    <row r="259" customFormat="1" s="2"/>
+    <row r="260" customFormat="1" s="2"/>
+    <row r="261" customFormat="1" s="2"/>
+    <row r="262" customFormat="1" s="2"/>
+    <row r="263" customFormat="1" s="2"/>
+    <row r="264" customFormat="1" s="2"/>
+    <row r="265" customFormat="1" s="2"/>
+    <row r="266" customFormat="1" s="2"/>
+    <row r="267" customFormat="1" s="2"/>
+    <row r="268" customFormat="1" s="2"/>
+    <row r="269" customFormat="1" s="2"/>
+    <row r="270" customFormat="1" s="2"/>
+    <row r="271" customFormat="1" s="2"/>
+    <row r="272" customFormat="1" s="2"/>
+    <row r="273" customFormat="1" s="2"/>
+    <row r="274" customFormat="1" s="2"/>
+    <row r="275" customFormat="1" s="2"/>
+    <row r="276" customFormat="1" s="2"/>
+    <row r="277" customFormat="1" s="2"/>
+    <row r="278" customFormat="1" s="2"/>
+    <row r="279" customFormat="1" s="2"/>
+    <row r="280" customFormat="1" s="2"/>
+    <row r="281" customFormat="1" s="2"/>
+    <row r="282" customFormat="1" s="2"/>
+    <row r="283" customFormat="1" s="2"/>
+    <row r="284" customFormat="1" s="2"/>
+    <row r="285" customFormat="1" s="2"/>
+    <row r="286" customFormat="1" s="2"/>
+    <row r="287" customFormat="1" s="2"/>
+    <row r="288" customFormat="1" s="2"/>
+    <row r="289" customFormat="1" s="2"/>
+    <row r="290" customFormat="1" s="2"/>
+    <row r="291" customFormat="1" s="2"/>
+    <row r="292" customFormat="1" s="2"/>
+    <row r="293" customFormat="1" s="2"/>
+    <row r="294" customFormat="1" s="2"/>
+    <row r="295" customFormat="1" s="2"/>
+    <row r="296" customFormat="1" s="2"/>
+    <row r="297" customFormat="1" s="2"/>
+    <row r="298" customFormat="1" s="2"/>
+    <row r="299" customFormat="1" s="2"/>
+    <row r="300" customFormat="1" s="2"/>
+    <row r="301" customFormat="1" s="2"/>
+    <row r="302" customFormat="1" s="2"/>
+    <row r="303" customFormat="1" s="2"/>
+    <row r="304" customFormat="1" s="2"/>
+    <row r="305" customFormat="1" s="2"/>
+    <row r="306" customFormat="1" s="2"/>
+    <row r="307" customFormat="1" s="2"/>
+    <row r="308" customFormat="1" s="2"/>
+    <row r="309" customFormat="1" s="2"/>
+    <row r="310" customFormat="1" s="2"/>
+    <row r="311" customFormat="1" s="2"/>
+    <row r="312" customFormat="1" s="2"/>
+    <row r="313" customFormat="1" s="2"/>
+    <row r="314" customFormat="1" s="2"/>
+    <row r="315" customFormat="1" s="2"/>
+    <row r="316" customFormat="1" s="2"/>
+    <row r="317" customFormat="1" s="2"/>
+    <row r="318" customFormat="1" s="2"/>
+    <row r="319" customFormat="1" s="2"/>
+    <row r="320" customFormat="1" s="2"/>
+    <row r="321" customFormat="1" s="2"/>
+    <row r="322" customFormat="1" s="2"/>
+    <row r="323" customFormat="1" s="2"/>
+    <row r="324" customFormat="1" s="2"/>
+    <row r="325" customFormat="1" s="2"/>
+    <row r="326" customFormat="1" s="2"/>
+    <row r="327" customFormat="1" s="2"/>
+    <row r="328" customFormat="1" s="2"/>
+    <row r="329" customFormat="1" s="2"/>
+    <row r="330" customFormat="1" s="2"/>
+    <row r="331" customFormat="1" s="2"/>
+    <row r="332" customFormat="1" s="2"/>
+    <row r="333" customFormat="1" s="2"/>
+    <row r="334" customFormat="1" s="2"/>
+    <row r="335" customFormat="1" s="2"/>
+    <row r="336" customFormat="1" s="2"/>
+    <row r="337" customFormat="1" s="2"/>
+    <row r="338" customFormat="1" s="2"/>
+    <row r="339" customFormat="1" s="2"/>
+    <row r="340" customFormat="1" s="2"/>
+    <row r="341" customFormat="1" s="2"/>
+    <row r="342" customFormat="1" s="2"/>
+    <row r="343" customFormat="1" s="2"/>
+    <row r="344" customFormat="1" s="2"/>
+    <row r="345" customFormat="1" s="2"/>
+    <row r="346" customFormat="1" s="2"/>
+    <row r="347" customFormat="1" s="2"/>
+    <row r="348" customFormat="1" s="2"/>
+    <row r="349" customFormat="1" s="2"/>
+    <row r="350" customFormat="1" s="2"/>
+    <row r="351" customFormat="1" s="2"/>
+    <row r="352" customFormat="1" s="2"/>
+    <row r="353" customFormat="1" s="2"/>
+    <row r="354" customFormat="1" s="2"/>
+    <row r="355" customFormat="1" s="2"/>
+    <row r="356" customFormat="1" s="2"/>
+    <row r="357" customFormat="1" s="2"/>
+    <row r="358" customFormat="1" s="2"/>
+    <row r="359" customFormat="1" s="2"/>
+    <row r="360" customFormat="1" s="2"/>
+    <row r="361" customFormat="1" s="2"/>
+    <row r="362" customFormat="1" s="2"/>
+    <row r="363" customFormat="1" s="2"/>
+    <row r="364" customFormat="1" s="2"/>
+    <row r="365" customFormat="1" s="2"/>
+    <row r="366" customFormat="1" s="2"/>
+    <row r="367" customFormat="1" s="2"/>
+    <row r="368" customFormat="1" s="2"/>
+    <row r="369" customFormat="1" s="2"/>
+    <row r="370" customFormat="1" s="2"/>
+    <row r="371" customFormat="1" s="2"/>
+    <row r="372" customFormat="1" s="2"/>
+    <row r="373" customFormat="1" s="2"/>
+    <row r="374" customFormat="1" s="2"/>
+    <row r="375" customFormat="1" s="2"/>
+    <row r="376" customFormat="1" s="2"/>
+    <row r="377" customFormat="1" s="2"/>
+    <row r="378" customFormat="1" s="2"/>
+    <row r="379" customFormat="1" s="2"/>
+    <row r="380" customFormat="1" s="2"/>
+    <row r="381" customFormat="1" s="2"/>
+    <row r="382" customFormat="1" s="2"/>
+    <row r="383" customFormat="1" s="2"/>
+    <row r="384" customFormat="1" s="2"/>
+    <row r="385" customFormat="1" s="2"/>
+    <row r="386" customFormat="1" s="2"/>
+    <row r="387" customFormat="1" s="2"/>
+    <row r="388" customFormat="1" s="2"/>
+    <row r="389" customFormat="1" s="2"/>
+    <row r="390" customFormat="1" s="2"/>
+    <row r="391" customFormat="1" s="2"/>
+    <row r="392" customFormat="1" s="2"/>
+    <row r="393" customFormat="1" s="2"/>
+    <row r="394" customFormat="1" s="2"/>
+    <row r="395" customFormat="1" s="2"/>
+    <row r="396" customFormat="1" s="2"/>
+    <row r="397" customFormat="1" s="2"/>
+    <row r="398" customFormat="1" s="2"/>
+    <row r="399" customFormat="1" s="2"/>
+    <row r="400" customFormat="1" s="2"/>
+    <row r="401" customFormat="1" s="2"/>
+    <row r="402" customFormat="1" s="2"/>
+    <row r="403" customFormat="1" s="2"/>
+    <row r="404" customFormat="1" s="2"/>
+    <row r="405" customFormat="1" s="2"/>
+    <row r="406" customFormat="1" s="2"/>
+    <row r="407" customFormat="1" s="2"/>
+    <row r="408" customFormat="1" s="2"/>
+    <row r="409" customFormat="1" s="2"/>
+    <row r="410" customFormat="1" s="2"/>
+    <row r="411" customFormat="1" s="2"/>
+    <row r="412" customFormat="1" s="2"/>
+    <row r="413" customFormat="1" s="2"/>
+    <row r="414" customFormat="1" s="2"/>
+    <row r="415" customFormat="1" s="2"/>
+    <row r="416" customFormat="1" s="2"/>
+    <row r="417" customFormat="1" s="2"/>
+    <row r="418" customFormat="1" s="2"/>
+    <row r="419" customFormat="1" s="2"/>
+    <row r="420" customFormat="1" s="2"/>
+    <row r="421" customFormat="1" s="2"/>
+    <row r="422" customFormat="1" s="2"/>
+    <row r="423" customFormat="1" s="2"/>
+    <row r="424" customFormat="1" s="2"/>
+    <row r="425" customFormat="1" s="2"/>
+    <row r="426" customFormat="1" s="2"/>
+    <row r="427" customFormat="1" s="2"/>
+    <row r="428" customFormat="1" s="2"/>
+    <row r="429" customFormat="1" s="2"/>
+    <row r="430" customFormat="1" s="2"/>
+    <row r="431" customFormat="1" s="2"/>
+    <row r="432" customFormat="1" s="2"/>
+    <row r="433" customFormat="1" s="2"/>
+    <row r="434" customFormat="1" s="2"/>
+    <row r="435" customFormat="1" s="2"/>
+    <row r="436" customFormat="1" s="2"/>
+    <row r="437" customFormat="1" s="2"/>
+    <row r="438" customFormat="1" s="2"/>
+    <row r="439" customFormat="1" s="2"/>
+    <row r="440" customFormat="1" s="2"/>
+    <row r="441" customFormat="1" s="2"/>
+    <row r="442" customFormat="1" s="2"/>
+    <row r="443" customFormat="1" s="2"/>
+    <row r="444" customFormat="1" s="2"/>
+    <row r="445" customFormat="1" s="2"/>
+    <row r="446" customFormat="1" s="2"/>
+    <row r="447" customFormat="1" s="2"/>
+    <row r="448" customFormat="1" s="2"/>
+    <row r="449" customFormat="1" s="2"/>
+    <row r="450" customFormat="1" s="2"/>
+    <row r="451" customFormat="1" s="2"/>
+    <row r="452" customFormat="1" s="2"/>
+    <row r="453" customFormat="1" s="2"/>
+    <row r="454" customFormat="1" s="2"/>
+    <row r="455" customFormat="1" s="2"/>
+    <row r="456" customFormat="1" s="2"/>
+    <row r="457" customFormat="1" s="2"/>
+    <row r="458" customFormat="1" s="2"/>
+    <row r="459" customFormat="1" s="2"/>
+    <row r="460" customFormat="1" s="2"/>
+    <row r="461" customFormat="1" s="2"/>
+    <row r="462" customFormat="1" s="2"/>
+    <row r="463" customFormat="1" s="2"/>
+    <row r="464" customFormat="1" s="2"/>
+    <row r="465" customFormat="1" s="2"/>
+    <row r="466" customFormat="1" s="2"/>
+    <row r="467" customFormat="1" s="2"/>
+    <row r="468" customFormat="1" s="2"/>
+    <row r="469" customFormat="1" s="2"/>
+    <row r="470" customFormat="1" s="2"/>
+    <row r="471" customFormat="1" s="2"/>
+    <row r="472" customFormat="1" s="2"/>
+    <row r="473" customFormat="1" s="2"/>
+    <row r="474" customFormat="1" s="2"/>
+    <row r="475" customFormat="1" s="2"/>
+    <row r="476" customFormat="1" s="2"/>
+    <row r="477" customFormat="1" s="2"/>
+    <row r="478" customFormat="1" s="2"/>
+    <row r="479" customFormat="1" s="2"/>
+    <row r="480" customFormat="1" s="2"/>
+    <row r="481" customFormat="1" s="2"/>
+    <row r="482" customFormat="1" s="2"/>
+    <row r="483" customFormat="1" s="2"/>
+    <row r="484" customFormat="1" s="2"/>
+    <row r="485" customFormat="1" s="2"/>
+    <row r="486" customFormat="1" s="2"/>
+    <row r="487" customFormat="1" s="2"/>
+    <row r="488" customFormat="1" s="2"/>
+    <row r="489" customFormat="1" s="2"/>
+    <row r="490" customFormat="1" s="2"/>
+    <row r="491" customFormat="1" s="2"/>
+    <row r="492" customFormat="1" s="2"/>
+    <row r="493" customFormat="1" s="2"/>
+    <row r="494" customFormat="1" s="2"/>
+    <row r="495" customFormat="1" s="2"/>
+    <row r="496" customFormat="1" s="2"/>
+    <row r="497" customFormat="1" s="2"/>
+    <row r="498" customFormat="1" s="2"/>
+    <row r="499" customFormat="1" s="2"/>
+    <row r="500" customFormat="1" s="2"/>
+    <row r="501" customFormat="1" s="2"/>
+    <row r="502" customFormat="1" s="2"/>
+    <row r="503" customFormat="1" s="2"/>
+    <row r="504" customFormat="1" s="2"/>
+    <row r="505" customFormat="1" s="2"/>
+    <row r="506" customFormat="1" s="2"/>
+    <row r="507" customFormat="1" s="2"/>
+    <row r="508" customFormat="1" s="2"/>
+    <row r="509" customFormat="1" s="2"/>
+    <row r="510" customFormat="1" s="2"/>
+    <row r="511" customFormat="1" s="2"/>
+    <row r="512" customFormat="1" s="2"/>
+    <row r="513" customFormat="1" s="2"/>
+    <row r="514" customFormat="1" s="2"/>
+    <row r="515" customFormat="1" s="2"/>
+    <row r="516" customFormat="1" s="2"/>
+    <row r="517" customFormat="1" s="2"/>
+    <row r="518" customFormat="1" s="2"/>
+    <row r="519" customFormat="1" s="2"/>
+    <row r="520" customFormat="1" s="2"/>
+    <row r="521" customFormat="1" s="2"/>
+    <row r="522" customFormat="1" s="2"/>
+    <row r="523" customFormat="1" s="2"/>
+    <row r="524" customFormat="1" s="2"/>
+    <row r="525" customFormat="1" s="2"/>
+    <row r="526" customFormat="1" s="2"/>
+    <row r="527" customFormat="1" s="2"/>
+    <row r="528" customFormat="1" s="2"/>
+    <row r="529" customFormat="1" s="2"/>
+    <row r="530" customFormat="1" s="2"/>
+    <row r="531" customFormat="1" s="2"/>
+    <row r="532" customFormat="1" s="2"/>
+    <row r="533" customFormat="1" s="2"/>
+    <row r="534" customFormat="1" s="2"/>
+    <row r="535" customFormat="1" s="2"/>
+    <row r="536" customFormat="1" s="2"/>
+    <row r="537" customFormat="1" s="2"/>
+    <row r="538" customFormat="1" s="2"/>
+    <row r="539" customFormat="1" s="2"/>
+    <row r="540" customFormat="1" s="2"/>
+    <row r="541" customFormat="1" s="2"/>
+    <row r="542" customFormat="1" s="2"/>
+    <row r="543" customFormat="1" s="2"/>
+    <row r="544" customFormat="1" s="2"/>
+    <row r="545" customFormat="1" s="2"/>
+    <row r="546" customFormat="1" s="2"/>
+    <row r="547" customFormat="1" s="2"/>
+    <row r="548" customFormat="1" s="2"/>
+    <row r="549" customFormat="1" s="2"/>
+    <row r="550" customFormat="1" s="2"/>
+    <row r="551" customFormat="1" s="2"/>
+    <row r="552" customFormat="1" s="2"/>
+    <row r="553" customFormat="1" s="2"/>
+    <row r="554" customFormat="1" s="2"/>
+    <row r="555" customFormat="1" s="2"/>
+    <row r="556" customFormat="1" s="2"/>
+    <row r="557" customFormat="1" s="2"/>
+    <row r="558" customFormat="1" s="2"/>
+    <row r="559" customFormat="1" s="2"/>
+    <row r="560" customFormat="1" s="2"/>
+    <row r="561" customFormat="1" s="2"/>
+    <row r="562" customFormat="1" s="2"/>
+    <row r="563" customFormat="1" s="2"/>
+    <row r="564" customFormat="1" s="2"/>
+    <row r="565" customFormat="1" s="2"/>
+    <row r="566" customFormat="1" s="2"/>
+    <row r="567" customFormat="1" s="2"/>
+    <row r="568" customFormat="1" s="2"/>
+    <row r="569" customFormat="1" s="2"/>
+    <row r="570" customFormat="1" s="2"/>
+    <row r="571" customFormat="1" s="2"/>
+    <row r="572" customFormat="1" s="2"/>
+    <row r="573" customFormat="1" s="2"/>
+    <row r="574" customFormat="1" s="2"/>
+    <row r="575" customFormat="1" s="2"/>
+    <row r="576" customFormat="1" s="2"/>
+    <row r="577" customFormat="1" s="2"/>
+    <row r="578" customFormat="1" s="2"/>
+    <row r="579" customFormat="1" s="2"/>
+    <row r="580" customFormat="1" s="2"/>
+    <row r="581" customFormat="1" s="2"/>
+    <row r="582" customFormat="1" s="2"/>
+    <row r="583" customFormat="1" s="2"/>
+    <row r="584" customFormat="1" s="2"/>
+    <row r="585" customFormat="1" s="2"/>
+    <row r="586" customFormat="1" s="2"/>
+    <row r="587" customFormat="1" s="2"/>
+    <row r="588" customFormat="1" s="2"/>
+    <row r="589" customFormat="1" s="2"/>
+    <row r="590" customFormat="1" s="2"/>
+    <row r="591" customFormat="1" s="2"/>
+    <row r="592" customFormat="1" s="2"/>
+    <row r="593" customFormat="1" s="2"/>
+    <row r="594" customFormat="1" s="2"/>
+    <row r="595" customFormat="1" s="2"/>
+    <row r="596" customFormat="1" s="2"/>
+    <row r="597" customFormat="1" s="2"/>
+    <row r="598" customFormat="1" s="2"/>
+    <row r="599" customFormat="1" s="2"/>
+    <row r="600" customFormat="1" s="2"/>
+    <row r="601" customFormat="1" s="2"/>
+    <row r="602" customFormat="1" s="2"/>
+    <row r="603" customFormat="1" s="2"/>
+    <row r="604" customFormat="1" s="2"/>
+    <row r="605" customFormat="1" s="2"/>
+    <row r="606" customFormat="1" s="2"/>
+    <row r="607" customFormat="1" s="2"/>
+    <row r="608" customFormat="1" s="2"/>
+    <row r="609" customFormat="1" s="2"/>
+    <row r="610" customFormat="1" s="2"/>
+    <row r="611" customFormat="1" s="2"/>
+    <row r="612" customFormat="1" s="2"/>
+    <row r="613" customFormat="1" s="2"/>
+    <row r="614" customFormat="1" s="2"/>
+    <row r="615" customFormat="1" s="2"/>
+    <row r="616" customFormat="1" s="2"/>
+    <row r="617" customFormat="1" s="2"/>
+    <row r="618" customFormat="1" s="2"/>
+    <row r="619" customFormat="1" s="2"/>
+    <row r="620" customFormat="1" s="2"/>
+    <row r="621" customFormat="1" s="2"/>
+    <row r="622" customFormat="1" s="2"/>
+    <row r="623" customFormat="1" s="2"/>
+    <row r="624" customFormat="1" s="2"/>
+    <row r="625" customFormat="1" s="2"/>
+    <row r="626" customFormat="1" s="2"/>
+    <row r="627" customFormat="1" s="2"/>
+    <row r="628" customFormat="1" s="2"/>
+    <row r="629" customFormat="1" s="2"/>
+    <row r="630" customFormat="1" s="2"/>
+    <row r="631" customFormat="1" s="2"/>
+    <row r="632" customFormat="1" s="2"/>
+    <row r="633" customFormat="1" s="2"/>
+    <row r="634" customFormat="1" s="2"/>
+    <row r="635" customFormat="1" s="2"/>
+    <row r="636" customFormat="1" s="2"/>
+    <row r="637" customFormat="1" s="2"/>
+    <row r="638" customFormat="1" s="2"/>
+    <row r="639" customFormat="1" s="2"/>
+    <row r="640" customFormat="1" s="2"/>
+    <row r="641" customFormat="1" s="2"/>
+    <row r="642" customFormat="1" s="2"/>
+    <row r="643" customFormat="1" s="2"/>
+    <row r="644" customFormat="1" s="2"/>
+    <row r="645" customFormat="1" s="2"/>
+    <row r="646" customFormat="1" s="2"/>
+    <row r="647" customFormat="1" s="2"/>
+    <row r="648" customFormat="1" s="2"/>
+    <row r="649" customFormat="1" s="2"/>
+    <row r="650" customFormat="1" s="2"/>
+    <row r="651" customFormat="1" s="2"/>
+    <row r="652" customFormat="1" s="2"/>
+    <row r="653" customFormat="1" s="2"/>
+    <row r="654" customFormat="1" s="2"/>
+    <row r="655" customFormat="1" s="2"/>
+    <row r="656" customFormat="1" s="2"/>
+    <row r="657" customFormat="1" s="2"/>
+    <row r="658" customFormat="1" s="2"/>
+    <row r="659" customFormat="1" s="2"/>
+    <row r="660" customFormat="1" s="2"/>
+    <row r="661" customFormat="1" s="2"/>
+    <row r="662" customFormat="1" s="2"/>
+    <row r="663" customFormat="1" s="2"/>
+    <row r="664" customFormat="1" s="2"/>
+    <row r="665" customFormat="1" s="2"/>
+    <row r="666" customFormat="1" s="2"/>
+    <row r="667" customFormat="1" s="2"/>
+    <row r="668" customFormat="1" s="2"/>
+    <row r="669" customFormat="1" s="2"/>
+    <row r="670" customFormat="1" s="2"/>
+    <row r="671" customFormat="1" s="2"/>
+    <row r="672" customFormat="1" s="2"/>
+    <row r="673" customFormat="1" s="2"/>
+    <row r="674" customFormat="1" s="2"/>
+    <row r="675" customFormat="1" s="2"/>
+    <row r="676" customFormat="1" s="2"/>
+    <row r="677" customFormat="1" s="2"/>
+    <row r="678" customFormat="1" s="2"/>
+    <row r="679" customFormat="1" s="2"/>
+    <row r="680" customFormat="1" s="2"/>
+    <row r="681" customFormat="1" s="2"/>
+    <row r="682" customFormat="1" s="2"/>
+    <row r="683" customFormat="1" s="2"/>
+    <row r="684" customFormat="1" s="2"/>
+    <row r="685" customFormat="1" s="2"/>
+    <row r="686" customFormat="1" s="2"/>
+    <row r="687" customFormat="1" s="2"/>
+    <row r="688" customFormat="1" s="2"/>
+    <row r="689" customFormat="1" s="2"/>
+    <row r="690" customFormat="1" s="2"/>
+    <row r="691" customFormat="1" s="2"/>
+    <row r="692" customFormat="1" s="2"/>
+    <row r="693" customFormat="1" s="2"/>
+    <row r="694" customFormat="1" s="2"/>
+    <row r="695" customFormat="1" s="2"/>
+    <row r="696" customFormat="1" s="2"/>
+    <row r="697" customFormat="1" s="2"/>
+    <row r="698" customFormat="1" s="2"/>
+    <row r="699" customFormat="1" s="2"/>
+    <row r="700" customFormat="1" s="2"/>
+    <row r="701" customFormat="1" s="2"/>
+    <row r="702" customFormat="1" s="2"/>
+    <row r="703" customFormat="1" s="2"/>
+    <row r="704" customFormat="1" s="2"/>
+    <row r="705" customFormat="1" s="2"/>
+    <row r="706" customFormat="1" s="2"/>
+    <row r="707" customFormat="1" s="2"/>
+    <row r="708" customFormat="1" s="2"/>
+    <row r="709" customFormat="1" s="2"/>
+    <row r="710" customFormat="1" s="2"/>
+    <row r="711" customFormat="1" s="2"/>
+    <row r="712" customFormat="1" s="2"/>
+    <row r="713" customFormat="1" s="2"/>
+    <row r="714" customFormat="1" s="2"/>
+    <row r="715" customFormat="1" s="2"/>
+    <row r="716" customFormat="1" s="2"/>
+    <row r="717" customFormat="1" s="2"/>
+    <row r="718" customFormat="1" s="2"/>
+    <row r="719" customFormat="1" s="2"/>
+    <row r="720" customFormat="1" s="2"/>
+    <row r="721" customFormat="1" s="2"/>
+    <row r="722" customFormat="1" s="2"/>
+    <row r="723" customFormat="1" s="2"/>
+    <row r="724" customFormat="1" s="2"/>
+    <row r="725" customFormat="1" s="2"/>
+    <row r="726" customFormat="1" s="2"/>
+    <row r="727" customFormat="1" s="2"/>
+    <row r="728" customFormat="1" s="2"/>
+    <row r="729" customFormat="1" s="2"/>
+    <row r="730" customFormat="1" s="2"/>
+    <row r="731" customFormat="1" s="2"/>
+    <row r="732" customFormat="1" s="2"/>
+    <row r="733" customFormat="1" s="2"/>
+    <row r="734" customFormat="1" s="2"/>
+    <row r="735" customFormat="1" s="2"/>
+    <row r="736" customFormat="1" s="2"/>
+    <row r="737" customFormat="1" s="2"/>
+    <row r="738" customFormat="1" s="2"/>
+    <row r="739" customFormat="1" s="2"/>
+    <row r="740" customFormat="1" s="2"/>
+    <row r="741" customFormat="1" s="2"/>
+    <row r="742" customFormat="1" s="2"/>
+    <row r="743" customFormat="1" s="2"/>
+    <row r="744" customFormat="1" s="2"/>
+    <row r="745" customFormat="1" s="2"/>
+    <row r="746" customFormat="1" s="2"/>
+    <row r="747" customFormat="1" s="2"/>
+    <row r="748" customFormat="1" s="2"/>
+    <row r="749" customFormat="1" s="2"/>
+    <row r="750" customFormat="1" s="2"/>
+    <row r="751" customFormat="1" s="2"/>
+    <row r="752" customFormat="1" s="2"/>
+    <row r="753" customFormat="1" s="2"/>
+    <row r="754" customFormat="1" s="2"/>
+    <row r="755" customFormat="1" s="2"/>
+    <row r="756" customFormat="1" s="2"/>
+    <row r="757" customFormat="1" s="2"/>
+    <row r="758" customFormat="1" s="2"/>
+    <row r="759" customFormat="1" s="2"/>
+    <row r="760" customFormat="1" s="2"/>
+    <row r="761" customFormat="1" s="2"/>
+    <row r="762" customFormat="1" s="2"/>
+    <row r="763" customFormat="1" s="2"/>
+    <row r="764" customFormat="1" s="2"/>
+    <row r="765" customFormat="1" s="2"/>
+    <row r="766" customFormat="1" s="2"/>
+    <row r="767" customFormat="1" s="2"/>
+    <row r="768" customFormat="1" s="2"/>
+    <row r="769" customFormat="1" s="2"/>
+    <row r="770" customFormat="1" s="2"/>
+    <row r="771" customFormat="1" s="2"/>
+    <row r="772" customFormat="1" s="2"/>
+    <row r="773" customFormat="1" s="2"/>
+    <row r="774" customFormat="1" s="2"/>
+    <row r="775" customFormat="1" s="2"/>
+    <row r="776" customFormat="1" s="2"/>
+    <row r="777" customFormat="1" s="2"/>
+    <row r="778" customFormat="1" s="2"/>
+    <row r="779" customFormat="1" s="2"/>
+    <row r="780" customFormat="1" s="2"/>
+    <row r="781" customFormat="1" s="2"/>
+    <row r="782" customFormat="1" s="2"/>
+    <row r="783" customFormat="1" s="2"/>
+    <row r="784" customFormat="1" s="2"/>
+    <row r="785" customFormat="1" s="2"/>
+    <row r="786" customFormat="1" s="2"/>
+    <row r="787" customFormat="1" s="2"/>
+    <row r="788" customFormat="1" s="2"/>
+    <row r="789" customFormat="1" s="2"/>
+    <row r="790" customFormat="1" s="2"/>
+    <row r="791" customFormat="1" s="2"/>
+    <row r="792" customFormat="1" s="2"/>
+    <row r="793" customFormat="1" s="2"/>
+    <row r="794" customFormat="1" s="2"/>
+    <row r="795" customFormat="1" s="2"/>
+    <row r="796" customFormat="1" s="2"/>
+    <row r="797" customFormat="1" s="2"/>
+    <row r="798" customFormat="1" s="2"/>
+    <row r="799" customFormat="1" s="2"/>
+    <row r="800" customFormat="1" s="2"/>
+    <row r="801" customFormat="1" s="2"/>
+    <row r="802" customFormat="1" s="2"/>
+    <row r="803" customFormat="1" s="2"/>
+    <row r="804" customFormat="1" s="2"/>
+    <row r="805" customFormat="1" s="2"/>
+    <row r="806" customFormat="1" s="2"/>
+    <row r="807" customFormat="1" s="2"/>
+    <row r="808" customFormat="1" s="2"/>
+    <row r="809" customFormat="1" s="2"/>
+    <row r="810" customFormat="1" s="2"/>
+    <row r="811" customFormat="1" s="2"/>
+    <row r="812" customFormat="1" s="2"/>
+    <row r="813" customFormat="1" s="2"/>
+    <row r="814" customFormat="1" s="2"/>
+    <row r="815" customFormat="1" s="2"/>
+    <row r="816" customFormat="1" s="2"/>
+    <row r="817" customFormat="1" s="2"/>
+    <row r="818" customFormat="1" s="2"/>
+    <row r="819" customFormat="1" s="2"/>
+    <row r="820" customFormat="1" s="2"/>
+    <row r="821" customFormat="1" s="2"/>
+    <row r="822" customFormat="1" s="2"/>
+    <row r="823" customFormat="1" s="2"/>
+    <row r="824" customFormat="1" s="2"/>
+    <row r="825" customFormat="1" s="2"/>
+    <row r="826" customFormat="1" s="2"/>
+    <row r="827" customFormat="1" s="2"/>
+    <row r="828" customFormat="1" s="2"/>
+    <row r="829" customFormat="1" s="2"/>
+    <row r="830" customFormat="1" s="2"/>
+    <row r="831" customFormat="1" s="2"/>
+    <row r="832" customFormat="1" s="2"/>
+    <row r="833" customFormat="1" s="2"/>
+    <row r="834" customFormat="1" s="2"/>
+    <row r="835" customFormat="1" s="2"/>
+    <row r="836" customFormat="1" s="2"/>
+    <row r="837" customFormat="1" s="2"/>
+    <row r="838" customFormat="1" s="2"/>
+    <row r="839" customFormat="1" s="2"/>
+    <row r="840" customFormat="1" s="2"/>
+    <row r="841" customFormat="1" s="2"/>
+    <row r="842" customFormat="1" s="2"/>
+    <row r="843" customFormat="1" s="2"/>
+    <row r="844" customFormat="1" s="2"/>
+    <row r="845" customFormat="1" s="2"/>
+    <row r="846" customFormat="1" s="2"/>
+    <row r="847" customFormat="1" s="2"/>
+    <row r="848" customFormat="1" s="2"/>
+    <row r="849" customFormat="1" s="2"/>
+    <row r="850" customFormat="1" s="2"/>
+    <row r="851" customFormat="1" s="2"/>
+    <row r="852" customFormat="1" s="2"/>
+    <row r="853" customFormat="1" s="2"/>
+    <row r="854" customFormat="1" s="2"/>
+    <row r="855" customFormat="1" s="2"/>
+    <row r="856" customFormat="1" s="2"/>
+    <row r="857" customFormat="1" s="2"/>
+    <row r="858" customFormat="1" s="2"/>
+    <row r="859" customFormat="1" s="2"/>
+    <row r="860" customFormat="1" s="2"/>
+    <row r="861" customFormat="1" s="2"/>
+    <row r="862" customFormat="1" s="2"/>
+    <row r="863" customFormat="1" s="2"/>
+    <row r="864" customFormat="1" s="2"/>
+    <row r="865" customFormat="1" s="2"/>
+    <row r="866" customFormat="1" s="2"/>
+    <row r="867" customFormat="1" s="2"/>
+    <row r="868" customFormat="1" s="2"/>
+    <row r="869" customFormat="1" s="2"/>
+    <row r="870" customFormat="1" s="2"/>
+    <row r="871" customFormat="1" s="2"/>
+    <row r="872" customFormat="1" s="2"/>
+    <row r="873" customFormat="1" s="2"/>
+    <row r="874" customFormat="1" s="2"/>
+    <row r="875" customFormat="1" s="2"/>
+    <row r="876" customFormat="1" s="2"/>
+    <row r="877" customFormat="1" s="2"/>
+    <row r="878" customFormat="1" s="2"/>
+    <row r="879" customFormat="1" s="2"/>
+    <row r="880" customFormat="1" s="2"/>
+    <row r="881" customFormat="1" s="2"/>
+    <row r="882" customFormat="1" s="2"/>
+    <row r="883" customFormat="1" s="2"/>
+    <row r="884" customFormat="1" s="2"/>
+    <row r="885" customFormat="1" s="2"/>
+    <row r="886" customFormat="1" s="2"/>
+    <row r="887" customFormat="1" s="2"/>
+    <row r="888" customFormat="1" s="2"/>
+    <row r="889" customFormat="1" s="2"/>
+    <row r="890" customFormat="1" s="2"/>
+    <row r="891" customFormat="1" s="2"/>
+    <row r="892" customFormat="1" s="2"/>
+    <row r="893" customFormat="1" s="2"/>
+    <row r="894" customFormat="1" s="2"/>
+    <row r="895" customFormat="1" s="2"/>
+    <row r="896" customFormat="1" s="2"/>
+    <row r="897" customFormat="1" s="2"/>
+    <row r="898" customFormat="1" s="2"/>
+    <row r="899" customFormat="1" s="2"/>
+    <row r="900" customFormat="1" s="2"/>
+    <row r="901" customFormat="1" s="2"/>
+    <row r="902" customFormat="1" s="2"/>
+    <row r="903" customFormat="1" s="2"/>
+    <row r="904" customFormat="1" s="2"/>
+    <row r="905" customFormat="1" s="2"/>
+    <row r="906" customFormat="1" s="2"/>
+    <row r="907" customFormat="1" s="2"/>
+    <row r="908" customFormat="1" s="2"/>
+    <row r="909" customFormat="1" s="2"/>
+    <row r="910" customFormat="1" s="2"/>
+    <row r="911" customFormat="1" s="2"/>
+    <row r="912" customFormat="1" s="2"/>
+    <row r="913" customFormat="1" s="2"/>
+    <row r="914" customFormat="1" s="2"/>
+    <row r="915" customFormat="1" s="2"/>
+    <row r="916" customFormat="1" s="2"/>
+    <row r="917" customFormat="1" s="2"/>
+    <row r="918" customFormat="1" s="2"/>
+    <row r="919" customFormat="1" s="2"/>
+    <row r="920" customFormat="1" s="2"/>
+    <row r="921" customFormat="1" s="2"/>
+    <row r="922" customFormat="1" s="2"/>
+    <row r="923" customFormat="1" s="2"/>
+    <row r="924" customFormat="1" s="2"/>
+    <row r="925" customFormat="1" s="2"/>
+    <row r="926" customFormat="1" s="2"/>
+    <row r="927" customFormat="1" s="2"/>
+    <row r="928" customFormat="1" s="2"/>
+    <row r="929" customFormat="1" s="2"/>
+    <row r="930" customFormat="1" s="2"/>
+    <row r="931" customFormat="1" s="2"/>
+    <row r="932" customFormat="1" s="2"/>
+    <row r="933" customFormat="1" s="2"/>
+    <row r="934" customFormat="1" s="2"/>
+    <row r="935" customFormat="1" s="2"/>
+    <row r="936" customFormat="1" s="2"/>
+    <row r="937" customFormat="1" s="2"/>
+    <row r="938" customFormat="1" s="2"/>
+    <row r="939" customFormat="1" s="2"/>
+    <row r="940" customFormat="1" s="2"/>
+    <row r="941" customFormat="1" s="2"/>
+    <row r="942" customFormat="1" s="2"/>
+    <row r="943" customFormat="1" s="2"/>
+    <row r="944" customFormat="1" s="2"/>
+    <row r="945" customFormat="1" s="2"/>
+    <row r="946" customFormat="1" s="2"/>
+    <row r="947" customFormat="1" s="2"/>
+    <row r="948" customFormat="1" s="2"/>
+    <row r="949" customFormat="1" s="2"/>
+    <row r="950" customFormat="1" s="2"/>
+    <row r="951" customFormat="1" s="2"/>
+    <row r="952" customFormat="1" s="2"/>
+    <row r="953" customFormat="1" s="2"/>
+    <row r="954" customFormat="1" s="2"/>
+    <row r="955" customFormat="1" s="2"/>
+    <row r="956" customFormat="1" s="2"/>
+    <row r="957" customFormat="1" s="2"/>
+    <row r="958" customFormat="1" s="2"/>
+    <row r="959" customFormat="1" s="2"/>
+    <row r="960" customFormat="1" s="2"/>
+    <row r="961" customFormat="1" s="2"/>
+    <row r="962" customFormat="1" s="2"/>
+    <row r="963" customFormat="1" s="2"/>
+    <row r="964" customFormat="1" s="2"/>
+    <row r="965" customFormat="1" s="2"/>
+    <row r="966" customFormat="1" s="2"/>
+    <row r="967" customFormat="1" s="2"/>
+    <row r="968" customFormat="1" s="2"/>
+    <row r="969" customFormat="1" s="2"/>
+    <row r="970" customFormat="1" s="2"/>
+    <row r="971" customFormat="1" s="2"/>
+    <row r="972" customFormat="1" s="2"/>
+    <row r="973" customFormat="1" s="2"/>
+    <row r="974" customFormat="1" s="2"/>
+    <row r="975" customFormat="1" s="2"/>
+    <row r="976" customFormat="1" s="2"/>
+    <row r="977" customFormat="1" s="2"/>
+    <row r="978" customFormat="1" s="2"/>
+    <row r="979" customFormat="1" s="2"/>
+    <row r="980" customFormat="1" s="2"/>
+    <row r="981" customFormat="1" s="2"/>
+    <row r="982" customFormat="1" s="2"/>
+    <row r="983" customFormat="1" s="2"/>
+    <row r="984" customFormat="1" s="2"/>
+    <row r="985" customFormat="1" s="2"/>
+    <row r="986" customFormat="1" s="2"/>
+    <row r="987" customFormat="1" s="2"/>
+    <row r="988" customFormat="1" s="2"/>
+    <row r="989" customFormat="1" s="2"/>
+    <row r="990" customFormat="1" s="2"/>
+    <row r="991" customFormat="1" s="2"/>
+    <row r="992" customFormat="1" s="2"/>
+    <row r="993" customFormat="1" s="2"/>
+    <row r="994" customFormat="1" s="2"/>
+    <row r="995" customFormat="1" s="2"/>
+    <row r="996" customFormat="1" s="2"/>
+    <row r="997" customFormat="1" s="2"/>
+    <row r="998" customFormat="1" s="2"/>
+    <row r="999" customFormat="1" s="2"/>
+    <row r="1000" customFormat="1" s="2"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>